--- a/GWD Data/Water Meter.xlsx
+++ b/GWD Data/Water Meter.xlsx
@@ -40,7 +40,7 @@
     <t>Label</t>
   </si>
   <si>
-    <t>Providing and fixing Water meter for Rigid PVC pipes, including jointing with PVC solvent cement-15 mm water met</t>
+    <t>Providing and fixing Water meter for Rigid PVC pipes, including jointing with PVC solvent cement-15 mm water meter</t>
   </si>
   <si>
     <t>Header Unit</t>
@@ -67,7 +67,7 @@
     <t>MR11005</t>
   </si>
   <si>
-    <t>Water Meter, Indian Standard, Class B, Multijet, 15mm ( ½? )</t>
+    <t>Water Meter, Indian Standard, Class B, Multijet, 15mm ( ½")</t>
   </si>
   <si>
     <t>each</t>
@@ -123,7 +123,7 @@
     <t>MR11006</t>
   </si>
   <si>
-    <t>Water Meter, Indian Standard, Class B, Multijet, 20mm ( ¾? )</t>
+    <t>Water Meter, Indian Standard, Class B, Multijet, 20mm ( ¾" )</t>
   </si>
 </sst>
 </file>

--- a/GWD Data/Water Meter.xlsx
+++ b/GWD Data/Water Meter.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Water Meter" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -129,42 +133,47 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Merriweather"/>
-    </font>
-    <font/>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Merriweather"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF212529"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF212529"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Merriweather"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -172,44 +181,52 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF212529"/>
-        <bgColor rgb="FF212529"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEE2E6"/>
-        <bgColor rgb="FFDEE2E6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="7">
-    <border/>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -218,6 +235,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -226,6 +245,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -243,6 +263,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -262,139 +283,314 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -535,22 +731,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" hidden="1" min="8" max="8" width="8.0"/>
-    <col customWidth="1" hidden="1" min="9" max="9" width="5.63"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29733565-E7F6-4039-8EE8-6FC9E81FB9A6}">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,32 +762,28 @@
         <v>3</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="12.75">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="12.75">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3"/>
@@ -600,33 +792,29 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="12.75">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="F4" s="12"/>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="12.75">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="3"/>
@@ -634,11 +822,9 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="12.75">
+      <c r="A6" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="3"/>
@@ -646,155 +832,137 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="12.75">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="12"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="10" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="12.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="11">
-        <v>875.0</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="D8" s="9">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>875</v>
+      </c>
+      <c r="F8" s="9">
         <f>D8*E8</f>
         <v>875</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="12.75">
+      <c r="A9" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <f>F8</f>
         <v>875</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="s">
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" ht="12.75">
+      <c r="A10" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="19" t="s">
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <f>F9/D9</f>
         <v>875</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="s">
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" ht="12.75">
+      <c r="A11" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9">
         <f>F10*1%</f>
         <v>8.75</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="s">
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" ht="12.75">
+      <c r="A12" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="11">
+      <c r="E12" s="15"/>
+      <c r="F12" s="9">
         <f>F11+F10</f>
         <v>883.75</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="s">
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" ht="12.75">
+      <c r="A13" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9">
         <f>F12*15%</f>
         <v>132.5625</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="s">
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" ht="12.75">
+      <c r="A14" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22">
-        <f>round(F13+F12,2)</f>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17">
+        <f>ROUND(F13+F12,2)</f>
         <v>1016.31</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="s">
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" ht="12.75">
+      <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="3"/>
@@ -802,192 +970,170 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="17">
-        <v>9999.0</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="13" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="12.75">
+      <c r="A16" s="13">
+        <v>9999</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="10" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="12.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="11">
-        <v>10.0</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="D17" s="9">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9">
         <v>2.12</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="9">
         <f>D17*E17</f>
-        <v>21.2</v>
-      </c>
-      <c r="G17" s="10" t="s">
+        <v>21.20</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17">
-        <v>9999.0</v>
-      </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="13" t="s">
+    </row>
+    <row r="18" spans="1:7" ht="12.75">
+      <c r="A18" s="13">
+        <v>9999</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="10" t="s">
+    </row>
+    <row r="19" spans="1:7" ht="12.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>9.36</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <v>2.12</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="9">
         <f>D19*E19</f>
         <v>19.8432</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="12.75">
+      <c r="A20" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="D20" s="9">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="9">
         <f>F19+F17</f>
-        <v>41.0432</v>
-      </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="s">
+        <v>41.043199999999999</v>
+      </c>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" spans="1:7" ht="12.75">
+      <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E21" s="19" t="s">
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="9">
         <f>F20/D20</f>
-        <v>41.0432</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="s">
+        <v>41.043199999999999</v>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:7" ht="12.75">
+      <c r="A22" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11">
+      <c r="E22" s="9"/>
+      <c r="F22" s="9">
         <f>F21*1%</f>
-        <v>0.410432</v>
-      </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="s">
+        <v>0.41043200000000002</v>
+      </c>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" spans="1:7" ht="12.75">
+      <c r="A23" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="11">
+      <c r="E23" s="15"/>
+      <c r="F23" s="9">
         <f>F22+F21</f>
-        <v>41.453632</v>
-      </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="s">
+        <v>41.453631999999999</v>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" ht="12.75">
+      <c r="A24" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11">
+      <c r="E24" s="9"/>
+      <c r="F24" s="9">
         <f>F23*15%</f>
-        <v>6.2180448</v>
-      </c>
-      <c r="G24" s="21"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="s">
+        <v>6.2180448000000004</v>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="1:7" ht="12.75">
+      <c r="A25" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22">
-        <f>round(F24+F23,2)</f>
+      <c r="E25" s="15"/>
+      <c r="F25" s="17">
+        <f>ROUND(F24+F23,2)</f>
         <v>47.67</v>
       </c>
-      <c r="G25" s="21"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="str">
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="1:7" ht="12.75">
+      <c r="A26" s="18" t="str">
         <f>CONCATENATE("Say ₹ ",F14," + ",F25," x Cost Index")</f>
         <v>Say ₹ 1016.31 + 47.67 x Cost Index</v>
       </c>
@@ -997,16 +1143,8 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="5">
-        <f>F8*1.01*1.15</f>
-        <v>1016.3125</v>
-      </c>
-      <c r="I26" s="5">
-        <f>(F17+F19)*1.01*1.15</f>
-        <v>47.6716768</v>
-      </c>
-    </row>
-    <row r="27">
+    </row>
+    <row r="27" spans="1:7" ht="12.75">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1022,32 +1160,28 @@
         <v>3</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="7" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="12.75">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="s">
+    </row>
+    <row r="29" spans="1:7" ht="12.75">
+      <c r="A29" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="3"/>
@@ -1056,33 +1190,29 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10" t="s">
+    </row>
+    <row r="30" spans="1:7" ht="12.75">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="F30" s="12"/>
+      <c r="E30" s="9">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="s">
+    </row>
+    <row r="31" spans="1:7" ht="12.75">
+      <c r="A31" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="3"/>
@@ -1090,11 +1220,9 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="12.75">
+      <c r="A32" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="3"/>
@@ -1102,155 +1230,137 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17" t="s">
+    </row>
+    <row r="33" spans="1:7" ht="12.75">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="10" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="12.75">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E34" s="11">
-        <v>1228.0</v>
-      </c>
-      <c r="F34" s="11">
+      <c r="D34" s="9">
+        <v>1</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1228</v>
+      </c>
+      <c r="F34" s="9">
         <f>D34*E34</f>
         <v>1228</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="s">
+    </row>
+    <row r="35" spans="1:7" ht="12.75">
+      <c r="A35" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E35" s="19" t="s">
+      <c r="D35" s="9">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="9">
         <f>F34</f>
         <v>1228</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="s">
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" spans="1:7" ht="12.75">
+      <c r="A36" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E36" s="19" t="s">
+      <c r="D36" s="9">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="9">
         <f>F35/D35</f>
         <v>1228</v>
       </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="s">
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" spans="1:7" ht="12.75">
+      <c r="A37" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11">
+      <c r="E37" s="9"/>
+      <c r="F37" s="9">
         <f>F36*1%</f>
         <v>12.28</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="s">
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" spans="1:7" ht="12.75">
+      <c r="A38" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="11">
+      <c r="E38" s="15"/>
+      <c r="F38" s="9">
         <f>F37+F36</f>
         <v>1240.28</v>
       </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="s">
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39" spans="1:7" ht="12.75">
+      <c r="A39" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11">
+      <c r="E39" s="9"/>
+      <c r="F39" s="9">
         <f>F38*15%</f>
         <v>186.042</v>
       </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="s">
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" spans="1:7" ht="12.75">
+      <c r="A40" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22">
-        <f>round(F39+F38,2)</f>
+      <c r="E40" s="15"/>
+      <c r="F40" s="17">
+        <f>ROUND(F39+F38,2)</f>
         <v>1426.32</v>
       </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="s">
+      <c r="G40" s="8"/>
+    </row>
+    <row r="41" spans="1:7" ht="12.75">
+      <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B41" s="3"/>
@@ -1258,192 +1368,170 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="17">
-        <v>9999.0</v>
-      </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="13" t="s">
+    </row>
+    <row r="42" spans="1:7" ht="12.75">
+      <c r="A42" s="13">
+        <v>9999</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="10"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="10" t="s">
+    </row>
+    <row r="43" spans="1:7" ht="12.75">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D43" s="11">
-        <v>10.0</v>
-      </c>
-      <c r="E43" s="11">
+      <c r="D43" s="9">
+        <v>10</v>
+      </c>
+      <c r="E43" s="9">
         <v>2.12</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="9">
         <f>D43*E43</f>
-        <v>21.2</v>
-      </c>
-      <c r="G43" s="10" t="s">
+        <v>21.20</v>
+      </c>
+      <c r="G43" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="17">
-        <v>9999.0</v>
-      </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="13" t="s">
+    </row>
+    <row r="44" spans="1:7" ht="12.75">
+      <c r="A44" s="13">
+        <v>9999</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="12"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="10" t="s">
+    </row>
+    <row r="45" spans="1:7" ht="12.75">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="9">
         <v>9.36</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="9">
         <v>2.12</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="9">
         <f>D45*E45</f>
         <v>19.8432</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="s">
+    </row>
+    <row r="46" spans="1:7" ht="12.75">
+      <c r="A46" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E46" s="19" t="s">
+      <c r="D46" s="9">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="9">
         <f>F45+F43</f>
-        <v>41.0432</v>
-      </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="s">
+        <v>41.043199999999999</v>
+      </c>
+      <c r="G46" s="15"/>
+    </row>
+    <row r="47" spans="1:7" ht="12.75">
+      <c r="A47" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E47" s="19" t="s">
+      <c r="D47" s="9">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="9">
         <f>F46/D46</f>
-        <v>41.0432</v>
-      </c>
-      <c r="G47" s="21"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="s">
+        <v>41.043199999999999</v>
+      </c>
+      <c r="G47" s="15"/>
+    </row>
+    <row r="48" spans="1:7" ht="12.75">
+      <c r="A48" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11">
+      <c r="E48" s="9"/>
+      <c r="F48" s="9">
         <f>F47*1%</f>
-        <v>0.410432</v>
-      </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="s">
+        <v>0.41043200000000002</v>
+      </c>
+      <c r="G48" s="15"/>
+    </row>
+    <row r="49" spans="1:7" ht="12.75">
+      <c r="A49" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="11">
+      <c r="E49" s="15"/>
+      <c r="F49" s="9">
         <f>F48+F47</f>
-        <v>41.453632</v>
-      </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="s">
+        <v>41.453631999999999</v>
+      </c>
+      <c r="G49" s="15"/>
+    </row>
+    <row r="50" spans="1:7" ht="12.75">
+      <c r="A50" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11">
+      <c r="E50" s="9"/>
+      <c r="F50" s="9">
         <f>F49*15%</f>
-        <v>6.2180448</v>
-      </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="s">
+        <v>6.2180448000000004</v>
+      </c>
+      <c r="G50" s="15"/>
+    </row>
+    <row r="51" spans="1:7" ht="12.75">
+      <c r="A51" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="22">
-        <f>round(F50+F49,2)</f>
+      <c r="E51" s="15"/>
+      <c r="F51" s="17">
+        <f>ROUND(F50+F49,2)</f>
         <v>47.67</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="str">
+      <c r="G51" s="15"/>
+    </row>
+    <row r="52" spans="1:7" ht="12.75">
+      <c r="A52" s="18" t="str">
         <f>CONCATENATE("Say ₹ ",F40," + ",F51," x Cost Index")</f>
         <v>Say ₹ 1426.32 + 47.67 x Cost Index</v>
       </c>
@@ -1453,14 +1541,6 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="5">
-        <f>F34*1.01*1.15</f>
-        <v>1426.322</v>
-      </c>
-      <c r="I52" s="5">
-        <f>(F43+F45)*1.01*1.15</f>
-        <v>47.6716768</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="68">
@@ -1533,6 +1613,6 @@
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="F42:G42"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/Water Meter.xlsx
+++ b/GWD Data/Water Meter.xlsx
@@ -742,7 +742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29733565-E7F6-4039-8EE8-6FC9E81FB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C910ADF-5459-4AFB-8F93-796267AEB9A6}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Water Meter.xlsx
+++ b/GWD Data/Water Meter.xlsx
@@ -742,7 +742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C910ADF-5459-4AFB-8F93-796267AEB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD18D2A4-EAFF-4D4B-A5EA-7DC49D3EB9A6}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
